--- a/hypatia/examples/Atlantis/sets/global.xlsx
+++ b/hypatia/examples/Atlantis/sets/global.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E916677-621C-4DDE-8C11-D68D08E445AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB8451F-13EE-4665-890C-DEDA31CE4E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sets" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="77">
   <si>
     <t>Year</t>
   </si>
@@ -258,6 +258,9 @@
   </si>
   <si>
     <t>Conversion</t>
+  </si>
+  <si>
+    <t>Y10</t>
   </si>
 </sst>
 </file>
@@ -378,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -406,11 +409,45 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="30">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0000000000"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -611,38 +648,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -854,8 +859,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Years" displayName="Years" ref="D1:E11" totalsRowShown="0" headerRowDxfId="29" headerRowBorderDxfId="28" tableBorderDxfId="27" totalsRowBorderDxfId="26">
-  <autoFilter ref="D1:E11" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Years" displayName="Years" ref="D1:E12" totalsRowShown="0" headerRowDxfId="29" headerRowBorderDxfId="28" tableBorderDxfId="27" totalsRowBorderDxfId="26">
+  <autoFilter ref="D1:E12" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="2">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Year" dataDxfId="25"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Year_name" dataDxfId="24"/>
@@ -865,8 +870,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Carriers_glob" displayName="Carriers_glob" ref="A21:D24" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A21:D24" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Carriers_glob" displayName="Carriers_glob" ref="A22:D25" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A22:D25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Carrier" dataDxfId="19"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Carr_name" dataDxfId="18"/>
@@ -881,34 +886,34 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Regions" displayName="Regions" ref="A1:B2" totalsRowShown="0">
   <autoFilter ref="A1:B2" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Region" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Region_name" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Region" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Region_name" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Technologies_glob" displayName="Technologies_glob" ref="A13:E18" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
-  <autoFilter ref="A13:E18" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Technologies_glob" displayName="Technologies_glob" ref="A14:E19" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+  <autoFilter ref="A14:E19" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Technology" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Tech_name" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Tech_category" dataDxfId="7"/>
-    <tableColumn id="1" xr3:uid="{F7E6113B-7421-48DB-83C7-8FFAA984C463}" name="Tech_cap_unit" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{3B7F032B-74C4-4B96-86A6-79EEAB4503A1}" name="Tech_act_unit" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Technology" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Tech_name" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Tech_category" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{F7E6113B-7421-48DB-83C7-8FFAA984C463}" name="Tech_cap_unit" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{3B7F032B-74C4-4B96-86A6-79EEAB4503A1}" name="Tech_act_unit" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Timesteps" displayName="Timesteps" ref="A27:C51" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A27:C51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Timesteps" displayName="Timesteps" ref="A28:C52" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A28:C52" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Timeslice" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Timeslice_name" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Timeslice_fraction" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Timeslice" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Timeslice_name" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Timeslice_fraction" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1189,21 +1194,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I51"/>
-  <sheetFormatPr defaultColWidth="8.62890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.62890625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.9453125" customWidth="1"/>
-    <col min="3" max="3" width="24.1015625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.3671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.62890625" customWidth="1"/>
-    <col min="6" max="6" width="13.1015625" customWidth="1"/>
-    <col min="7" max="7" width="16.47265625" customWidth="1"/>
-    <col min="8" max="8" width="17.89453125" customWidth="1"/>
-    <col min="9" max="9" width="16.3671875" customWidth="1"/>
+    <col min="1" max="1" width="30.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.90625" customWidth="1"/>
+    <col min="3" max="3" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6328125" customWidth="1"/>
+    <col min="6" max="6" width="13.08984375" customWidth="1"/>
+    <col min="7" max="7" width="16.453125" customWidth="1"/>
+    <col min="8" max="8" width="17.90625" customWidth="1"/>
+    <col min="9" max="9" width="16.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1226,11 +1231,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>59</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1249,7 +1254,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
       <c r="D3" s="5" t="s">
         <v>60</v>
       </c>
@@ -1257,7 +1264,9 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
       <c r="D4" s="5" t="s">
         <v>61</v>
       </c>
@@ -1265,7 +1274,9 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
       <c r="D5" s="5" t="s">
         <v>62</v>
       </c>
@@ -1273,7 +1284,9 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
       <c r="D6" s="5" t="s">
         <v>63</v>
       </c>
@@ -1281,7 +1294,9 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
       <c r="D7" s="5" t="s">
         <v>64</v>
       </c>
@@ -1289,7 +1304,9 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
       <c r="D8" s="5" t="s">
         <v>65</v>
       </c>
@@ -1297,7 +1314,9 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
       <c r="D9" s="5" t="s">
         <v>66</v>
       </c>
@@ -1305,7 +1324,9 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
       <c r="D10" s="5" t="s">
         <v>67</v>
       </c>
@@ -1313,7 +1334,9 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
       <c r="D11" s="5" t="s">
         <v>68</v>
       </c>
@@ -1321,70 +1344,63 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="3" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="D12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="5" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="5" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>55</v>
@@ -1393,15 +1409,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>16</v>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>55</v>
@@ -1410,15 +1426,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>8</v>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>55</v>
@@ -1427,347 +1443,364 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="3" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="1" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="7" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B28" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="8"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="1">
+      <c r="F28" s="8"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
         <v>1</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="E28" s="8"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="1">
+      <c r="C29" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
         <v>2</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="1">
+      <c r="C30" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
         <v>3</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="1">
+      <c r="C31" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
         <v>4</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="1">
+      <c r="C32" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="1">
         <v>5</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="E32" s="8"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="1">
+      <c r="C33" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E33" s="8"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="1">
         <v>6</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="1">
+      <c r="C34" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="1">
         <v>7</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="1">
+      <c r="C35" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="1">
         <v>8</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="1">
+      <c r="C36" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="1">
         <v>9</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="1">
+      <c r="C37" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="1">
         <v>10</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C37" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="1">
+      <c r="C38" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="1">
         <v>11</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C38" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="1">
+      <c r="C39" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="1">
         <v>12</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C39" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="1">
+      <c r="C40" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="1">
         <v>13</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="1">
+      <c r="C41" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="1">
         <v>14</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C41" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="1">
+      <c r="C42" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="1">
         <v>15</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="1">
+      <c r="C43" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="1">
         <v>16</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="1">
+      <c r="C44" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="1">
         <v>17</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="1">
+      <c r="C45" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="1">
         <v>18</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C45" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="1">
+      <c r="C46" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" s="1">
         <v>19</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="1">
+      <c r="C47" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="1">
         <v>20</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="1">
+      <c r="C48" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="1">
         <v>21</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C48" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="1">
+      <c r="C49" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="1">
         <v>22</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="1">
+      <c r="C50" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="1">
         <v>23</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C50" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="1">
+      <c r="C51" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="1">
         <v>24</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C52" s="10">
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -1787,15 +1820,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e">
@@ -1812,6 +1836,15 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2070,14 +2103,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{400CE890-4FAA-43FF-AB05-78D100D91AC8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82347752-6D50-4565-8A47-C3BD006EDCEE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2088,6 +2113,29 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{400CE890-4FAA-43FF-AB05-78D100D91AC8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F571C89-B126-4182-8FAD-79E7F0190403}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F571C89-B126-4182-8FAD-79E7F0190403}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e"/>
+    <ds:schemaRef ds:uri="e67e9a88-35e1-4b39-8da9-a609eb308282"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>